--- a/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
+++ b/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
@@ -687,6 +687,9 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
@@ -695,6 +698,9 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
@@ -702,6 +708,9 @@
     <row r="5">
       <c r="A5" t="s">
         <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>

--- a/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
+++ b/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
@@ -13,13 +13,16 @@
     <sheet name="2-row-vertical-merge" sheetId="4" r:id="rId7"/>
     <sheet name="2-row-bidirectional-merge" sheetId="5" r:id="rId8"/>
     <sheet name="2-row-horizontal-merge-repeated" sheetId="6" r:id="rId9"/>
+    <sheet name="2-row-vertical-merge-repeated" sheetId="7" r:id="rId10"/>
+    <sheet name="2-row-bidirectional-merge-rep" sheetId="8" r:id="rId11"/>
+    <sheet name="2-row-mixed-merge" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>group1</t>
   </si>
@@ -115,6 +118,72 @@
   </si>
   <si>
     <t>r5cG</t>
+  </si>
+  <si>
+    <t>r3cH</t>
+  </si>
+  <si>
+    <t>r4cH</t>
+  </si>
+  <si>
+    <t>r5cH</t>
+  </si>
+  <si>
+    <t>r3cI</t>
+  </si>
+  <si>
+    <t>r4cI</t>
+  </si>
+  <si>
+    <t>r5cI</t>
+  </si>
+  <si>
+    <t>groupA</t>
+  </si>
+  <si>
+    <t>groupB</t>
+  </si>
+  <si>
+    <t>groupC</t>
+  </si>
+  <si>
+    <t>headerJ</t>
+  </si>
+  <si>
+    <t>headerH</t>
+  </si>
+  <si>
+    <t>headerI</t>
+  </si>
+  <si>
+    <t>headerK</t>
+  </si>
+  <si>
+    <t>r3cJ</t>
+  </si>
+  <si>
+    <t>r4cJ</t>
+  </si>
+  <si>
+    <t>r5cJ</t>
+  </si>
+  <si>
+    <t>r3cK</t>
+  </si>
+  <si>
+    <t>r4cK</t>
+  </si>
+  <si>
+    <t>r5cK</t>
+  </si>
+  <si>
+    <t>r3cL</t>
+  </si>
+  <si>
+    <t>r4cL</t>
+  </si>
+  <si>
+    <t>r5cL</t>
   </si>
 </sst>
 </file>
@@ -836,4 +905,383 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="F1:H2"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
+++ b/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="2-row-simple" sheetId="1" r:id="rId1"/>
-    <sheet name="2-row-empty-cell" sheetId="2" r:id="rId5"/>
-    <sheet name="2-row-horizontal-merge" sheetId="3" r:id="rId6"/>
-    <sheet name="2-row-vertical-merge" sheetId="4" r:id="rId7"/>
-    <sheet name="2-row-bidirectional-merge" sheetId="5" r:id="rId8"/>
-    <sheet name="2-row-horizontal-merge-repeated" sheetId="6" r:id="rId9"/>
-    <sheet name="2-row-vertical-merge-repeated" sheetId="7" r:id="rId10"/>
-    <sheet name="2-row-bidirectional-merge-rep" sheetId="8" r:id="rId11"/>
-    <sheet name="2-row-mixed-merge" sheetId="9" r:id="rId12"/>
+    <sheet name="2-row-duplicate-header" sheetId="2" r:id="rId5"/>
+    <sheet name="2-row-empty-cell" sheetId="3" r:id="rId6"/>
+    <sheet name="2-row-horizontal-merge" sheetId="4" r:id="rId7"/>
+    <sheet name="2-row-vertical-merge" sheetId="5" r:id="rId8"/>
+    <sheet name="2-row-bidirectional-merge" sheetId="6" r:id="rId9"/>
+    <sheet name="2-row-horizontal-merge-repeated" sheetId="7" r:id="rId10"/>
+    <sheet name="2-row-vertical-merge-repeated" sheetId="8" r:id="rId11"/>
+    <sheet name="2-row-bidirectional-merge-rep" sheetId="9" r:id="rId12"/>
+    <sheet name="2-row-mixed-merge" sheetId="10" r:id="rId13"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -549,6 +550,180 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+  </mergeCells>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -557,8 +732,11 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -569,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -666,9 +844,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
 </worksheet>
 </file>
 
@@ -678,16 +853,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
@@ -730,7 +905,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -743,11 +918,17 @@
       <c r="A1" t="s">
         <v>3</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
@@ -787,7 +968,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -798,36 +979,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -840,18 +1000,6 @@
       <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -863,18 +1011,6 @@
       <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -886,23 +1022,10 @@
       <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:F1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -913,24 +1036,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2">
       <c r="B2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" t="s">
         <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -949,6 +1084,12 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -966,6 +1107,12 @@
       <c r="E4" t="s">
         <v>24</v>
       </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -983,12 +1130,17 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:F1"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1001,18 +1153,21 @@
       <c r="A1" t="s">
         <v>3</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2">
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1032,18 +1187,6 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -1061,18 +1204,6 @@
       <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -1090,24 +1221,12 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D2"/>
-    <mergeCell ref="F1:H2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -1117,49 +1236,22 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="s">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" t="s">
-        <v>41</v>
+      <c r="F1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -1190,15 +1282,6 @@
       <c r="I3" t="s">
         <v>35</v>
       </c>
-      <c r="J3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -1228,15 +1311,6 @@
       <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -1266,22 +1340,12 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="J5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D2"/>
+    <mergeCell ref="F1:H2"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
+++ b/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
@@ -199,15 +199,20 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -215,12 +220,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,57 +517,57 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -555,162 +580,172 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2" t="s">
         <v>53</v>
       </c>
     </row>
@@ -729,57 +764,57 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -792,54 +827,55 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -852,54 +888,55 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -915,54 +952,55 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -978,48 +1016,51 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1035,105 +1076,109 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1150,75 +1195,79 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="E1" s="1"/>
     </row>
     <row r="2">
-      <c r="B2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1236,108 +1285,121 @@
   <dimension ref="A1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2">
-      <c r="E2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I2" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="2" t="s">
         <v>37</v>
       </c>
     </row>

--- a/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
+++ b/excel/testdata/schema_header_2row/schema_header_2row_tests.xlsx
@@ -193,10 +193,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
